--- a/documentation/Project Acceptance Test.xlsx
+++ b/documentation/Project Acceptance Test.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jb00645\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jb00645\Desktop\Lab 9 DevOps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A1F3D2-096E-499A-AE80-9D8D107F23EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12383DA5-7AA8-4AB0-B643-E099DE721343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="0" windowWidth="25800" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,140 +25,163 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="42">
-  <si>
-    <t>Given…</t>
-  </si>
-  <si>
-    <t>When…</t>
-  </si>
-  <si>
-    <t>Then…</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="47">
   <si>
     <t>I am logged in to my account</t>
   </si>
   <si>
-    <t>I click the "Upload" button and select a project file</t>
-  </si>
-  <si>
     <t>The project file is uploaded successfully and stored in my portfolio</t>
   </si>
   <si>
     <t>I have multiple projects uploaded</t>
   </si>
   <si>
-    <t>I select a category from the list and assign it to a project</t>
-  </si>
-  <si>
-    <t>The project is categorized under the selected category</t>
-  </si>
-  <si>
     <t>I have a project uploaded</t>
   </si>
   <si>
-    <t>I click on the project title</t>
-  </si>
-  <si>
     <t>The individual project page displays the full details of the project</t>
   </si>
   <si>
-    <t>I have logged in and accessed the portfolio settings</t>
-  </si>
-  <si>
-    <t>I change the layout, colors, or content of my portfolio</t>
-  </si>
-  <si>
     <t>My portfolio is updated with the new customizations</t>
   </si>
   <si>
-    <t>I have multiple projects uploaded with categories and tags</t>
-  </si>
-  <si>
-    <t>I select a filter for category or tag</t>
-  </si>
-  <si>
-    <t>The displayed projects match the selected category or tag filter</t>
-  </si>
-  <si>
     <t>I have a hosted project URL</t>
   </si>
   <si>
-    <t>I paste the URL in the project’s hosted link section</t>
-  </si>
-  <si>
     <t>The hosted project link is added and clickable on the project page</t>
   </si>
   <si>
     <t>I have an existing project</t>
   </si>
   <si>
-    <t>I select "Edit" or "Delete" from the project options</t>
-  </si>
-  <si>
-    <t>The project is either updated or removed from my portfolio</t>
-  </si>
-  <si>
     <t>I have a project that needs repository links</t>
   </si>
   <si>
-    <t>I paste the repository URL or attach resources</t>
-  </si>
-  <si>
     <t>The repository link and resources are successfully added to the project page</t>
   </si>
   <si>
-    <t>I select the visibility option (public or private) for the project</t>
-  </si>
-  <si>
-    <t>The project’s visibility setting is updated accordingly</t>
-  </si>
-  <si>
-    <t>I am on the registration page</t>
-  </si>
-  <si>
-    <t>I enter my information and submit the form</t>
-  </si>
-  <si>
-    <t>My account is created, and I can start uploading projects</t>
-  </si>
-  <si>
-    <t>I set up two-factor authentication</t>
-  </si>
-  <si>
-    <t>My account is secured with an extra layer of authentication</t>
-  </si>
-  <si>
     <t>I have customized my portfolio</t>
   </si>
   <si>
-    <t>I click the "Preview" button</t>
-  </si>
-  <si>
-    <t>My portfolio displays exactly as it would to others</t>
-  </si>
-  <si>
-    <t>I access my portfolio on a mobile device or desktop</t>
-  </si>
-  <si>
-    <t>I navigate to the project page</t>
-  </si>
-  <si>
-    <t>The project page adjusts appropriately to the screen size and device</t>
-  </si>
-  <si>
     <t>I access the dashboard</t>
   </si>
   <si>
     <t>The dashboard displays all of my projects with options to organize, edit, or delete them</t>
+  </si>
+  <si>
+    <t>Given...</t>
+  </si>
+  <si>
+    <t>When...</t>
+  </si>
+  <si>
+    <t>Then...</t>
+  </si>
+  <si>
+    <t>I enter valid username, password, and email, then submit the form</t>
+  </si>
+  <si>
+    <t>My account is created and I can start uploading projects</t>
+  </si>
+  <si>
+    <t>I leave required fields blank or provide invalid email format</t>
+  </si>
+  <si>
+    <t>An error message is displayed and the account is not created</t>
+  </si>
+  <si>
+    <t>I click the "Upload" button and select a valid project file</t>
+  </si>
+  <si>
+    <t>I attempt to upload a file in an unsupported format</t>
+  </si>
+  <si>
+    <t>I paste a valid URL in the project’s hosted link section</t>
+  </si>
+  <si>
+    <t>I select "Edit" from the project options and update the title and description</t>
+  </si>
+  <si>
+    <t>The project is updated with the new information</t>
+  </si>
+  <si>
+    <t>I select "Edit" and leave required fields blank</t>
+  </si>
+  <si>
+    <t>I select "Delete" from the project options</t>
+  </si>
+  <si>
+    <t>The project is removed from my portfolio</t>
+  </si>
+  <si>
+    <t>I paste a valid GitHub or GitLab URL</t>
+  </si>
+  <si>
+    <t>I paste an invalid or incomplete repository URL</t>
+  </si>
+  <si>
+    <t>I am on the create account page</t>
+  </si>
+  <si>
+    <t>The file is not uploaded</t>
+  </si>
+  <si>
+    <t>I click on the view project</t>
+  </si>
+  <si>
+    <t>I change the layout or content of my portfolio</t>
+  </si>
+  <si>
+    <t>I have logged in and accessed the account portfolio settings</t>
+  </si>
+  <si>
+    <t>I select a filter for name or user name</t>
+  </si>
+  <si>
+    <t>The displayed projects match the selected filters</t>
+  </si>
+  <si>
+    <t>I paste incorrect link</t>
+  </si>
+  <si>
+    <t>No Link Provided appears</t>
+  </si>
+  <si>
+    <t>Temp data is saved as place holders (i.e. No Link Provided)</t>
+  </si>
+  <si>
+    <t>I click the "Save" button</t>
+  </si>
+  <si>
+    <t>My portfolio displays updated information</t>
+  </si>
+  <si>
+    <t>I click the "Cancel" button</t>
+  </si>
+  <si>
+    <t>My portfolio displays most recent saved information</t>
+  </si>
+  <si>
+    <t>I select "Cancel" and leave required fields blank</t>
+  </si>
+  <si>
+    <t>My Project displays most recent saved information</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -175,18 +198,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -194,102 +217,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -571,186 +512,227 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="61.08984375" customWidth="1"/>
-    <col min="2" max="2" width="61" customWidth="1"/>
+    <col min="2" max="2" width="69.6328125" customWidth="1"/>
     <col min="3" max="3" width="78.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
+      <c r="B8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="9" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
+      <c r="B11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="8" t="s">
+    </row>
+    <row r="16" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="12" t="s">
+      <c r="B17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="4"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" s="1"/>
+    </row>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
